--- a/assets/ESR Formations-England.xlsx
+++ b/assets/ESR Formations-England.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{1387204D-2BDB-4948-B700-406CBBECFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C70088-6333-40EF-8DEE-AC9FBA4FD574}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{1387204D-2BDB-4948-B700-406CBBECFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE83BF9-4B19-4FC7-A510-64189CA66F2F}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="525" windowWidth="26610" windowHeight="14700" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="660" yWindow="240" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
   <si>
     <t>Formation</t>
   </si>
@@ -124,18 +124,9 @@
     <t>x</t>
   </si>
   <si>
-    <t>Brigade</t>
-  </si>
-  <si>
     <t>Foot Infantry Battalions</t>
   </si>
   <si>
-    <t>Infantry Division</t>
-  </si>
-  <si>
-    <t>1st Division</t>
-  </si>
-  <si>
     <t>Foot Guards Battalions</t>
   </si>
   <si>
@@ -145,9 +136,6 @@
     <t>Limit one 1st Division</t>
   </si>
   <si>
-    <t>Light Division</t>
-  </si>
-  <si>
     <t>Light Foot Battalions</t>
   </si>
   <si>
@@ -160,21 +148,12 @@
     <t>Limit one Light Division</t>
   </si>
   <si>
-    <t>Light Cavalry Brigade</t>
-  </si>
-  <si>
     <t>Light Dragoon Squadron Groups</t>
   </si>
   <si>
-    <t>[Heavy] Cavalry Brigade</t>
-  </si>
-  <si>
     <t>Dragoon Squadron Groups</t>
   </si>
   <si>
-    <t>Artillery Park</t>
-  </si>
-  <si>
     <t>9-pdr Royal Artillery Battery</t>
   </si>
   <si>
@@ -182,10 +161,6 @@
   </si>
   <si>
     <t>6-pdr Royal Horse Artillery Battery</t>
-  </si>
-  <si>
-    <t>Impetuous
-Rapid Deployment</t>
   </si>
   <si>
     <r>
@@ -213,49 +188,78 @@
     <t>Infantry Company</t>
   </si>
   <si>
-    <t>Foot Guards BR</t>
-  </si>
-  <si>
-    <t>Life Guards BR</t>
-  </si>
-  <si>
-    <t>Royal Horse Guards BR</t>
-  </si>
-  <si>
-    <t>Light Infantry BR</t>
-  </si>
-  <si>
-    <t>Foot Infantry BR</t>
-  </si>
-  <si>
-    <t>Highland Foot Inf BR</t>
-  </si>
-  <si>
-    <t>Fusilier Foot Infantry BR</t>
-  </si>
-  <si>
-    <t>Rifles BR</t>
-  </si>
-  <si>
-    <t>Dragoon Guards BR</t>
-  </si>
-  <si>
-    <t>Dragoons BR</t>
-  </si>
-  <si>
-    <t>Light Dragoons BR</t>
-  </si>
-  <si>
-    <t>Hussars BR</t>
-  </si>
-  <si>
-    <t>9-pdr Royal Artillery BR</t>
-  </si>
-  <si>
-    <t>6-pdr Royal Artillery BR</t>
-  </si>
-  <si>
-    <t>6-pdr Royal Horse Artillery BR</t>
+    <t>BR Foot Guards</t>
+  </si>
+  <si>
+    <t>BR Life Guards</t>
+  </si>
+  <si>
+    <t>BR Royal Horse Guards</t>
+  </si>
+  <si>
+    <t>BR Light Infantry</t>
+  </si>
+  <si>
+    <t>BR Foot Infantry</t>
+  </si>
+  <si>
+    <t>BR Highland Foot Inf</t>
+  </si>
+  <si>
+    <t>BR Fusilier Foot Infantry</t>
+  </si>
+  <si>
+    <t>BR Rifles</t>
+  </si>
+  <si>
+    <t>BR Dragoon Guards</t>
+  </si>
+  <si>
+    <t>BR Dragoons</t>
+  </si>
+  <si>
+    <t>BR Light Dragoons</t>
+  </si>
+  <si>
+    <t>BR Hussars</t>
+  </si>
+  <si>
+    <t>BR 9-pdr Royal Artillery</t>
+  </si>
+  <si>
+    <t>BR 6-pdr Royal Artillery</t>
+  </si>
+  <si>
+    <t>BR 6-pdr Royal Horse Artillery</t>
+  </si>
+  <si>
+    <t>BR Brigade</t>
+  </si>
+  <si>
+    <t>BR Infantry Division</t>
+  </si>
+  <si>
+    <t>BR 1st Division</t>
+  </si>
+  <si>
+    <t>BR Light Division</t>
+  </si>
+  <si>
+    <t>BR Light Cavalry Brigade</t>
+  </si>
+  <si>
+    <t>BR Heavy Cavalry Brigade</t>
+  </si>
+  <si>
+    <t>BR Artillery Park</t>
+  </si>
+  <si>
+    <t>Impetuous,
+Rapid Deployment</t>
+  </si>
+  <si>
+    <t>Impetuous, 
+Rapid Deployment</t>
   </si>
 </sst>
 </file>
@@ -733,21 +737,21 @@
         <v>5</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3">
         <v>3</v>
@@ -757,19 +761,19 @@
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3">
         <v>5</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>10</v>
@@ -777,22 +781,22 @@
     </row>
     <row r="4" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>11</v>
@@ -800,13 +804,13 @@
     </row>
     <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3">
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>11</v>
@@ -814,13 +818,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>10</v>
@@ -828,22 +832,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>10</v>
@@ -851,13 +855,13 @@
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3">
         <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>10</v>
@@ -865,13 +869,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>10</v>
@@ -879,45 +883,45 @@
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E11" s="3">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>11</v>
@@ -925,7 +929,7 @@
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>11</v>
@@ -933,7 +937,7 @@
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -942,13 +946,13 @@
         <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>11</v>
@@ -956,13 +960,13 @@
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>11</v>
@@ -970,13 +974,13 @@
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>12</v>
@@ -984,7 +988,7 @@
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I16" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>12</v>
@@ -992,7 +996,7 @@
     </row>
     <row r="17" spans="9:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I17" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>12</v>
@@ -1028,55 +1032,55 @@
       </c>
       <c r="D1" s="3" t="str" cm="1">
         <f t="array" ref="D1:R1">TRANSPOSE( BaselineFormations!I3:I17 )</f>
-        <v>Foot Guards BR</v>
+        <v>BR Foot Guards</v>
       </c>
       <c r="E1" s="3" t="str">
-        <v>Life Guards BR</v>
+        <v>BR Life Guards</v>
       </c>
       <c r="F1" s="3" t="str">
-        <v>Royal Horse Guards BR</v>
+        <v>BR Royal Horse Guards</v>
       </c>
       <c r="G1" s="3" t="str">
-        <v>Light Infantry BR</v>
+        <v>BR Light Infantry</v>
       </c>
       <c r="H1" s="3" t="str">
-        <v>Foot Infantry BR</v>
+        <v>BR Foot Infantry</v>
       </c>
       <c r="I1" s="3" t="str">
-        <v>Highland Foot Inf BR</v>
+        <v>BR Highland Foot Inf</v>
       </c>
       <c r="J1" s="3" t="str">
-        <v>Fusilier Foot Infantry BR</v>
+        <v>BR Fusilier Foot Infantry</v>
       </c>
       <c r="K1" s="3" t="str">
-        <v>Rifles BR</v>
+        <v>BR Rifles</v>
       </c>
       <c r="L1" s="3" t="str">
-        <v>Dragoon Guards BR</v>
+        <v>BR Dragoon Guards</v>
       </c>
       <c r="M1" s="3" t="str">
-        <v>Dragoons BR</v>
+        <v>BR Dragoons</v>
       </c>
       <c r="N1" s="3" t="str">
-        <v>Light Dragoons BR</v>
+        <v>BR Light Dragoons</v>
       </c>
       <c r="O1" s="3" t="str">
-        <v>Hussars BR</v>
+        <v>BR Hussars</v>
       </c>
       <c r="P1" s="3" t="str">
-        <v>9-pdr Royal Artillery BR</v>
+        <v>BR 9-pdr Royal Artillery</v>
       </c>
       <c r="Q1" s="3" t="str">
-        <v>6-pdr Royal Artillery BR</v>
+        <v>BR 6-pdr Royal Artillery</v>
       </c>
       <c r="R1" s="3" t="str">
-        <v>6-pdr Royal Horse Artillery BR</v>
+        <v>BR 6-pdr Royal Horse Artillery</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:C8">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
-        <v>Brigade</v>
+        <v>BR Brigade</v>
       </c>
       <c r="B2" t="str">
         <v>Infantry</v>
@@ -1087,10 +1091,22 @@
       <c r="H2" t="s">
         <v>14</v>
       </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <v>Infantry Division</v>
+        <v>BR Infantry Division</v>
       </c>
       <c r="B3" t="str">
         <v>Infantry</v>
@@ -1101,16 +1117,22 @@
       <c r="H3" t="s">
         <v>14</v>
       </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
       <c r="P3" t="s">
         <v>14</v>
       </c>
       <c r="Q3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>1st Division</v>
+        <v>BR 1st Division</v>
       </c>
       <c r="B4" t="str">
         <v>Infantry</v>
@@ -1130,16 +1152,22 @@
       <c r="I4" t="s">
         <v>14</v>
       </c>
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
       <c r="P4" t="s">
         <v>14</v>
       </c>
       <c r="Q4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>Light Division</v>
+        <v>BR Light Division</v>
       </c>
       <c r="B5" t="str">
         <v>Infantry</v>
@@ -1165,13 +1193,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>Light Cavalry Brigade</v>
+        <v>BR Light Cavalry Brigade</v>
       </c>
       <c r="B6" t="str">
         <v>Cavalry</v>
       </c>
       <c r="C6" t="str">
-        <v>Impetuous
+        <v>Impetuous, 
 Rapid Deployment</v>
       </c>
       <c r="N6" t="s">
@@ -1183,13 +1211,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>[Heavy] Cavalry Brigade</v>
+        <v>BR Heavy Cavalry Brigade</v>
       </c>
       <c r="B7" t="str">
         <v>Cavalry</v>
       </c>
       <c r="C7" t="str">
-        <v>Impetuous
+        <v>Impetuous,
 Rapid Deployment</v>
       </c>
       <c r="M7" t="s">
@@ -1201,7 +1229,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>Artillery Park</v>
+        <v>BR Artillery Park</v>
       </c>
       <c r="B8" t="str">
         <v>Artillery</v>

--- a/assets/ESR Formations-England.xlsx
+++ b/assets/ESR Formations-England.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{1387204D-2BDB-4948-B700-406CBBECFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE83BF9-4B19-4FC7-A510-64189CA66F2F}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{1387204D-2BDB-4948-B700-406CBBECFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6205CD2D-6DAB-482D-920D-19D8AEAA7379}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="240" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="2190" yWindow="1605" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t>Formation</t>
   </si>
@@ -260,6 +260,12 @@
   <si>
     <t>Impetuous, 
 Rapid Deployment</t>
+  </si>
+  <si>
+    <t>BR Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -392,6 +398,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1013,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="24.85546875" customWidth="1"/>
@@ -1077,36 +1087,63 @@
         <v>BR 6-pdr Royal Horse Artillery</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C8">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C9">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>BR Brigade</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Infantry</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>BR Infantry Division</v>
       </c>
       <c r="B3" t="str">
         <v>Infantry</v>
@@ -1132,7 +1169,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>BR 1st Division</v>
+        <v>BR Infantry Division</v>
       </c>
       <c r="B4" t="str">
         <v>Infantry</v>
@@ -1140,16 +1177,7 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
         <v>14</v>
       </c>
       <c r="K4" t="s">
@@ -1167,7 +1195,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>BR Light Division</v>
+        <v>BR 1st Division</v>
       </c>
       <c r="B5" t="str">
         <v>Infantry</v>
@@ -1175,7 +1203,16 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="G5" t="s">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="K5" t="s">
@@ -1193,57 +1230,83 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
+        <v>BR Light Division</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Infantry</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
         <v>BR Light Cavalry Brigade</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C7" t="str">
         <v>Impetuous, 
 Rapid Deployment</v>
       </c>
-      <c r="N6" t="s">
-        <v>14</v>
-      </c>
-      <c r="R6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+      <c r="R7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
         <v>BR Heavy Cavalry Brigade</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B8" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C8" t="str">
         <v>Impetuous,
 Rapid Deployment</v>
       </c>
-      <c r="M7" t="s">
-        <v>14</v>
-      </c>
-      <c r="R7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
         <v>BR Artillery Park</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B9" t="str">
         <v>Artillery</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C9" t="str">
         <v>Reinforcements</v>
       </c>
-      <c r="P8" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>14</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="P9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R9" t="s">
         <v>14</v>
       </c>
     </row>
